--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20241.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="47">
   <si>
     <t>Mat</t>
   </si>
@@ -100,97 +100,64 @@
     <t>ESCOBAR</t>
   </si>
   <si>
-    <t>ARMAS</t>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>MENCIAS</t>
   </si>
   <si>
     <t>FERNANDEZ</t>
   </si>
   <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
+    <t>VILLEGAS</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>MENCIAS</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
     <t>JUAN</t>
   </si>
   <si>
-    <t>SALINAS</t>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>JORGE</t>
   </si>
   <si>
     <t>MARQUEZ</t>
   </si>
   <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
+    <t>CORONA</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
     <t>GIOVANNI ARIEL</t>
   </si>
   <si>
-    <t>JOSE GUSTAVO</t>
+    <t>JESUS ANTONIO</t>
+  </si>
+  <si>
+    <t>ALEXIS URIEL</t>
+  </si>
+  <si>
+    <t>JAVIER</t>
   </si>
   <si>
     <t>CRISTAL</t>
   </si>
   <si>
-    <t>ARELI CICLARI</t>
-  </si>
-  <si>
-    <t>LUZ ELENA</t>
+    <t>MAURICIO</t>
   </si>
   <si>
     <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>JESUS ANTONIO</t>
-  </si>
-  <si>
-    <t>JAVIER</t>
-  </si>
-  <si>
-    <t>MAURICIO</t>
-  </si>
-  <si>
-    <t>JOSMAR</t>
-  </si>
-  <si>
-    <t>SANDRA PAOLA</t>
   </si>
 </sst>
 </file>
@@ -864,16 +831,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>77.5</v>
+      </c>
+      <c r="H2">
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -887,16 +857,19 @@
         <v>48</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>48</v>
       </c>
-      <c r="E3">
-        <v>48</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>7.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -910,16 +883,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>97.22</v>
+      </c>
+      <c r="H4">
+        <v>8.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -933,16 +909,19 @@
         <v>40</v>
       </c>
       <c r="D5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>77.5</v>
+      </c>
+      <c r="H5">
+        <v>6.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -956,16 +935,19 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>82.34999999999999</v>
+      </c>
+      <c r="H6">
+        <v>7.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -979,16 +961,19 @@
         <v>33</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>78.79000000000001</v>
+      </c>
+      <c r="H7">
+        <v>6.7</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1002,16 +987,19 @@
         <v>23</v>
       </c>
       <c r="D8">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>82.61</v>
+      </c>
+      <c r="H8">
+        <v>6.9</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1025,16 +1013,19 @@
         <v>19</v>
       </c>
       <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
         <v>19</v>
       </c>
-      <c r="E9">
-        <v>19</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
       <c r="G9">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H9">
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1048,16 +1039,19 @@
         <v>36</v>
       </c>
       <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
         <v>36</v>
       </c>
-      <c r="E10">
-        <v>36</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
       <c r="G10">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H10">
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -1113,16 +1107,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>80</v>
+        <v>77.5</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1139,16 +1133,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G3">
-        <v>97.92</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1174,7 +1168,7 @@
         <v>97.22</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1191,16 +1185,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>62.5</v>
+        <v>77.5</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1217,13 +1211,13 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>73.53</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H6">
         <v>7.4</v>
@@ -1243,16 +1237,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G7">
-        <v>69.7</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H7">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1269,16 +1263,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G8">
-        <v>78.26000000000001</v>
+        <v>82.61</v>
       </c>
       <c r="H8">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1304,7 +1298,7 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1330,7 +1324,7 @@
         <v>100</v>
       </c>
       <c r="H10">
-        <v>8.9</v>
+        <v>9.4</v>
       </c>
     </row>
   </sheetData>
@@ -1340,7 +1334,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1378,10 +1372,10 @@
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1395,22 +1389,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920304</v>
+        <v>24330051920026</v>
       </c>
       <c r="B3" t="s">
         <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1418,22 +1412,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920152</v>
+        <v>24330051920137</v>
       </c>
       <c r="B4" t="s">
         <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1441,185 +1435,93 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920217</v>
+        <v>24330051920140</v>
       </c>
       <c r="B5" t="s">
         <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920244</v>
+        <v>24330051920152</v>
       </c>
       <c r="B6" t="s">
         <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920396</v>
+        <v>23330051920343</v>
       </c>
       <c r="B7" t="s">
         <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920026</v>
+        <v>24330051920396</v>
       </c>
       <c r="B8" t="s">
         <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>24330051920140</v>
-      </c>
-      <c r="B9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>23330051920343</v>
-      </c>
-      <c r="B10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>24330051920125</v>
-      </c>
-      <c r="B11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>24330051920184</v>
-      </c>
-      <c r="B12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" t="s">
-        <v>57</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20241.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20241.xlsx
@@ -103,12 +103,12 @@
     <t>IXMATLAHUA</t>
   </si>
   <si>
+    <t>MENCIAS</t>
+  </si>
+  <si>
     <t>RUIZ</t>
   </si>
   <si>
-    <t>MENCIAS</t>
-  </si>
-  <si>
     <t>FERNANDEZ</t>
   </si>
   <si>
@@ -124,12 +124,12 @@
     <t>CALIHUA</t>
   </si>
   <si>
+    <t>JORGE</t>
+  </si>
+  <si>
     <t>SANTOS</t>
   </si>
   <si>
-    <t>JORGE</t>
-  </si>
-  <si>
     <t>MARQUEZ</t>
   </si>
   <si>
@@ -145,10 +145,10 @@
     <t>JESUS ANTONIO</t>
   </si>
   <si>
+    <t>JAVIER</t>
+  </si>
+  <si>
     <t>ALEXIS URIEL</t>
-  </si>
-  <si>
-    <t>JAVIER</t>
   </si>
   <si>
     <t>CRISTAL</t>
@@ -1412,7 +1412,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920137</v>
+        <v>24330051920140</v>
       </c>
       <c r="B4" t="s">
         <v>28</v>
@@ -1430,12 +1430,12 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920140</v>
+        <v>24330051920137</v>
       </c>
       <c r="B5" t="s">
         <v>29</v>

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20241.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="69">
   <si>
     <t>Mat</t>
   </si>
@@ -97,6 +97,30 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>PICHARDO</t>
+  </si>
+  <si>
     <t>ESCOBAR</t>
   </si>
   <si>
@@ -118,6 +142,30 @@
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>PINO</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>TLATEMOHUE</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
     <t>JUAN</t>
   </si>
   <si>
@@ -136,7 +184,28 @@
     <t>CORONA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>EDILBERTO</t>
+  </si>
+  <si>
+    <t>YARETZY NAOMI</t>
+  </si>
+  <si>
+    <t>ANGEL ISMAEL</t>
+  </si>
+  <si>
+    <t>BRYAN</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>JANNIHA YUVIETH</t>
+  </si>
+  <si>
+    <t>JIMENA</t>
   </si>
   <si>
     <t>GIOVANNI ARIEL</t>
@@ -155,9 +224,6 @@
   </si>
   <si>
     <t>MAURICIO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
   </si>
 </sst>
 </file>
@@ -1334,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1366,16 +1432,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920103</v>
+        <v>24330051920326</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1384,113 +1450,113 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920026</v>
+        <v>24330051920410</v>
       </c>
       <c r="B3" t="s">
         <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920140</v>
+        <v>24330051920247</v>
       </c>
       <c r="B4" t="s">
         <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920137</v>
+        <v>24330051920239</v>
       </c>
       <c r="B5" t="s">
         <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920152</v>
+        <v>24330051920274</v>
       </c>
       <c r="B6" t="s">
         <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920343</v>
+        <v>24330051920127</v>
       </c>
       <c r="B7" t="s">
         <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1499,29 +1565,213 @@
         <v>14</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920396</v>
+        <v>24330051920388</v>
       </c>
       <c r="B8" t="s">
         <v>32</v>
       </c>
       <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>24330051920316</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>24330051920103</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>24330051920026</v>
+      </c>
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>24330051920140</v>
+      </c>
+      <c r="B12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>24330051920137</v>
+      </c>
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>24330051920152</v>
+      </c>
+      <c r="B14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>23330051920343</v>
+      </c>
+      <c r="B15" t="s">
         <v>39</v>
       </c>
-      <c r="D8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="C15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>24330051920396</v>
+      </c>
+      <c r="B16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
         <v>16</v>
       </c>
-      <c r="G8">
+      <c r="G16">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20241.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="26">
   <si>
     <t>Mat</t>
   </si>
@@ -95,135 +95,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>PICHARDO</t>
-  </si>
-  <si>
-    <t>ESCOBAR</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>MENCIAS</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>FERNANDEZ</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>PINO</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>TLATEMOHUE</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>JUAN</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>EDILBERTO</t>
-  </si>
-  <si>
-    <t>YARETZY NAOMI</t>
-  </si>
-  <si>
-    <t>ANGEL ISMAEL</t>
-  </si>
-  <si>
-    <t>BRYAN</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>JANNIHA YUVIETH</t>
-  </si>
-  <si>
-    <t>JIMENA</t>
-  </si>
-  <si>
-    <t>GIOVANNI ARIEL</t>
-  </si>
-  <si>
-    <t>JESUS ANTONIO</t>
-  </si>
-  <si>
-    <t>JAVIER</t>
-  </si>
-  <si>
-    <t>ALEXIS URIEL</t>
-  </si>
-  <si>
-    <t>CRISTAL</t>
-  </si>
-  <si>
-    <t>MAURICIO</t>
   </si>
 </sst>
 </file>
@@ -1173,16 +1044,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G2">
-        <v>77.5</v>
+        <v>97.5</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1208,7 +1079,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1234,7 +1105,7 @@
         <v>97.22</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1251,13 +1122,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G5">
-        <v>77.5</v>
+        <v>97.5</v>
       </c>
       <c r="H5">
         <v>6.8</v>
@@ -1277,16 +1148,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G6">
-        <v>82.34999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1303,13 +1174,13 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>78.79000000000001</v>
+        <v>90.91</v>
       </c>
       <c r="H7">
         <v>6.9</v>
@@ -1329,16 +1200,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G8">
-        <v>82.61</v>
+        <v>100</v>
       </c>
       <c r="H8">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1364,7 +1235,7 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1390,7 +1261,7 @@
         <v>100</v>
       </c>
       <c r="H10">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1400,7 +1271,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1430,351 +1301,6 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>24330051920326</v>
-      </c>
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>24330051920410</v>
-      </c>
-      <c r="B3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>24330051920247</v>
-      </c>
-      <c r="B4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>24330051920239</v>
-      </c>
-      <c r="B5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>24330051920274</v>
-      </c>
-      <c r="B6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>24330051920127</v>
-      </c>
-      <c r="B7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>24330051920388</v>
-      </c>
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>24330051920316</v>
-      </c>
-      <c r="B9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>24330051920103</v>
-      </c>
-      <c r="B10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" t="s">
-        <v>63</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>24330051920026</v>
-      </c>
-      <c r="B11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>24330051920140</v>
-      </c>
-      <c r="B12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" t="s">
-        <v>65</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>24330051920137</v>
-      </c>
-      <c r="B13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" t="s">
-        <v>66</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>24330051920152</v>
-      </c>
-      <c r="B14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" t="s">
-        <v>67</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>23330051920343</v>
-      </c>
-      <c r="B15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" t="s">
-        <v>54</v>
-      </c>
-      <c r="D15" t="s">
-        <v>68</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>24330051920396</v>
-      </c>
-      <c r="B16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" t="s">
-        <v>55</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
